--- a/docs/Mapping_casi_uso/matrimoni/Matr_003.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_003.xlsx
@@ -767,7 +767,7 @@
     <t>evento.datiEventoMatrimonio.padreSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(2,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,2,4,5)</t>
   </si>
   <si>
     <t>Padre Sposa</t>
@@ -776,7 +776,7 @@
     <t>evento.datiEventoMatrimonio.padreSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(2,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,2,4,5)</t>
   </si>
   <si>
     <t>Madre Sposo</t>
@@ -785,7 +785,7 @@
     <t>evento.datiEventoMatrimonio.madreSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,4,5)</t>
   </si>
   <si>
     <t>Madre Sposa</t>
@@ -794,7 +794,7 @@
     <t>evento.datiEventoMatrimonio.madreSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,4,5)</t>
   </si>
   <si>
     <t>Tutore Sposo</t>
@@ -803,13 +803,13 @@
     <t>evento.datiEventoMatrimonio.assistenteLegaleSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3,5)</t>
   </si>
   <si>
     <t>Curatore Sposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3,4)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3,4)</t>
   </si>
   <si>
     <t>Nomina Legale Sposo</t>
@@ -818,7 +818,7 @@
     <t>evento.datiEventoMatrimonio.nominaAssistenteLegaleSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3)</t>
   </si>
   <si>
     <t>Tutore Sposa</t>
@@ -827,13 +827,13 @@
     <t>evento.datiEventoMatrimonio.assistenteLegaleSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3,5)</t>
   </si>
   <si>
     <t>Curatore Sposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3,4)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3,4)</t>
   </si>
   <si>
     <t>Nomina Legale Sposa</t>
@@ -842,7 +842,7 @@
     <t>evento.datiEventoMatrimonio.nominaAssistenteLegaleSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3)</t>
   </si>
   <si>
     <t>Interprete</t>
@@ -929,13 +929,13 @@
     <t>attoNotarile</t>
   </si>
   <si>
-    <t>Assistenza minore Sposo</t>
+    <t>Assistenza Sposo</t>
   </si>
   <si>
     <t>tipoAssistenteSposo</t>
   </si>
   <si>
-    <t>Assistenza minore Sposa</t>
+    <t>Assistenza Sposa</t>
   </si>
   <si>
     <t>tipoAssistenteSposa</t>
@@ -1039,7 +1039,7 @@
     <col min="4" max="4" width="59.5078125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="32.48828125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="27.3203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="218.19921875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="114.08984375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9465,10 +9465,10 @@
         <v>249</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D367" s="2" t="s">
         <v>250</v>
@@ -10109,10 +10109,10 @@
         <v>252</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D395" s="2" t="s">
         <v>253</v>
@@ -10753,10 +10753,10 @@
         <v>255</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D423" s="2" t="s">
         <v>256</v>
@@ -11397,10 +11397,10 @@
         <v>258</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D451" s="2" t="s">
         <v>259</v>
@@ -12041,10 +12041,10 @@
         <v>261</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="C479" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D479" s="2" t="s">
         <v>262</v>
@@ -12685,10 +12685,10 @@
         <v>264</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="C507" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D507" s="2" t="s">
         <v>262</v>
@@ -13490,10 +13490,10 @@
         <v>269</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="C542" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D542" s="2" t="s">
         <v>270</v>
@@ -14134,10 +14134,10 @@
         <v>272</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="C570" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D570" s="2" t="s">
         <v>270</v>
@@ -15227,7 +15227,7 @@
         <v>306</v>
       </c>
       <c r="F617" s="2" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="G617" s="2" t="s">
         <v>55</v>
